--- a/data/output/workbook/2026-07-08.xlsx
+++ b/data/output/workbook/2026-07-08.xlsx
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10353675"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 03:35</t>
+          <t>2026-07-08 11:28</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,250 +3031,171 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Seattle Mariners offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.945</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.346</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.945</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.8</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.694</v>
+        <v>4.346</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.312</v>
+        <v>7.854</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -3338,22 +3259,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.082</v>
+        <v>7.694</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.646000000000001</v>
+        <v>1.312</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3417,313 +3338,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>1.082</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.449</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.133</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.608</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q74" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Seattle Mariners defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.716</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.716</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>5th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.033</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.979</v>
+        <v>3.967</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.918</v>
+        <v>8.286</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -3787,22 +3708,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.958</v>
+        <v>7.979</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.816</v>
+        <v>0.918</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3866,68 +3787,147 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.333</v>
+        <v>0.958</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.608</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="H81" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.397</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6754,7 +6754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6771,246 +6771,167 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.512</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.679</v>
-      </c>
-      <c r="Q68" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.512</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.533</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>8.106</v>
+        <v>4.679</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.213</v>
+        <v>7.234</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -7074,22 +6995,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.383</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.426</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -7153,313 +7074,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.404</v>
+        <v>1.383</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H73" s="33" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.545</v>
       </c>
-      <c r="Q72" s="34" t="inlineStr">
+      <c r="Q73" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>3.949</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.829</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.404</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.949</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.9</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>9.319000000000001</v>
+        <v>4.829</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.213</v>
+        <v>7.404</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -7523,22 +7444,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.17</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>9.532</v>
+        <v>1.213</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -7602,72 +7523,151 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>9.532</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.545</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H80" s="33" t="inlineStr">
+      <c r="H81" s="33" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="J81" s="33" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>1.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.595</v>
       </c>
-      <c r="Q80" s="34" t="inlineStr">
+      <c r="Q81" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8846,7 +8846,7 @@
         <v>-170</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5976</v>
+        <v>0.5627</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-149</v>
+        <v>-129</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8968,17 +8968,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6425000000000001</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-180</v>
+        <v>-239</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>150</v>
+        <v>-114</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -180). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9014,37 +9014,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.7108</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-130</v>
+        <v>-246</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>174</v>
+        <v>-122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 71.1% (fair -246). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9085,12 +9085,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9100,17 +9100,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4353</v>
+        <v>0.4522</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9146,37 +9146,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4481</v>
+        <v>0.2095</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>123</v>
+        <v>377</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 21.0% (fair +377). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9212,37 +9212,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.2095</v>
+        <v>0.4617</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>377</v>
+        <v>117</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 21.0% (fair +377). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9283,12 +9283,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9298,17 +9298,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4024</v>
+        <v>0.4373</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9364,17 +9364,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4244</v>
+        <v>0.6421</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>136</v>
+        <v>-179</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>160</v>
+        <v>-127</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9415,32 +9415,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Golden State Valkyries @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4617</v>
+        <v>0.2916</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 29.2% (fair +243). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9542,12 +9542,12 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Indiana Fever @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9557,22 +9557,22 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +9.5</t>
+          <t>Over 183.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5261</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-125</v>
+        <v>-111</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries @ Toronto Tempo</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.302</v>
+        <v>0.4244</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>257</v>
+        <v>156</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9679,32 +9679,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5383</v>
+        <v>0.4701</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-117</v>
+        <v>113</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9740,17 +9740,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9760,17 +9760,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4841</v>
+        <v>0.5762</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>107</v>
+        <v>-136</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>122</v>
+        <v>-117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9811,32 +9811,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.485</v>
+        <v>0.5756</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>106</v>
+        <v>-136</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>120</v>
+        <v>-117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5008</v>
+        <v>0.5009</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>-100</v>
@@ -9938,17 +9938,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.2433</v>
+        <v>0.4903</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>311</v>
+        <v>104</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>335</v>
+        <v>117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 24.3% (fair +311). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5492</v>
+        <v>0.5513</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-108</v>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10075,32 +10075,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5802</v>
+        <v>0.3705</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-138</v>
+        <v>170</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-122</v>
+        <v>186</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 37.0% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10141,32 +10141,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Los Angeles Sparks</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 184.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5199</v>
+        <v>0.4986</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10207,32 +10207,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5756</v>
+        <v>0.5085</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>-103</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-120</v>
+        <v>107</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10268,37 +10268,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Seattle Storm +10.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5039</v>
+        <v>0.5261</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10334,37 +10334,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4737</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10400,37 +10400,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 175.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-118</v>
+        <v>-149</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-108</v>
+        <v>-132</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4961</v>
+        <v>0.5014000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>102</v>
+        <v>-101</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10697,13 +10697,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5039</v>
+        <v>0.4986</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10759,17 +10759,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.46445</v>
+        <v>0.462</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10825,17 +10825,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.43685</v>
+        <v>0.538</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>129</v>
+        <v>-116</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10895,13 +10895,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4573</v>
+        <v>0.4588</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10961,10 +10961,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5427</v>
+        <v>0.5412</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-117</v>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11023,17 +11023,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5488</v>
+        <v>0.4726</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-122</v>
+        <v>112</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11089,17 +11089,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4512</v>
+        <v>0.5274</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>122</v>
+        <v>-112</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3575</v>
+        <v>0.3579</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +180). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11225,13 +11225,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6425000000000001</v>
+        <v>0.6421</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-180</v>
+        <v>-179</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>150</v>
+        <v>-127</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -180). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11291,13 +11291,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3902</v>
+        <v>0.4016999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6098</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-156</v>
+        <v>-149</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-148</v>
+        <v>-132</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
@@ -11429,7 +11429,7 @@
         <v>-144</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11485,17 +11485,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.32655</v>
+        <v>0.4097499999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 32.7% (fair +206). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11561,7 +11561,7 @@
         <v>117</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11627,7 +11627,7 @@
         <v>-117</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11687,10 +11687,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4508</v>
+        <v>0.4487</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>108</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11753,10 +11753,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5492</v>
+        <v>0.5513</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-108</v>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11815,17 +11815,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.497</v>
+        <v>0.5085</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>101</v>
+        <v>-103</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-104</v>
+        <v>107</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11881,17 +11881,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4174</v>
+        <v>0.4915</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11951,13 +11951,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4353</v>
+        <v>0.4373</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12017,13 +12017,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5627</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.515</v>
+        <v>0.5097</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12149,13 +12149,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.485</v>
+        <v>0.4903</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12215,13 +12215,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4864000000000001</v>
+        <v>0.4772999999999999</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -12338,22 +12338,22 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5835</v>
+        <v>0.4638</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-140</v>
+        <v>116</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-138</v>
+        <v>108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -12404,22 +12404,22 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4165</v>
+        <v>0.5362</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>140</v>
+        <v>-116</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>133</v>
+        <v>-110</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12470,19 +12470,19 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4523</v>
+        <v>0.52785</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>121</v>
+        <v>-112</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>117</v>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12536,22 +12536,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5477</v>
+        <v>0.47215</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-121</v>
+        <v>112</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-117</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12602,22 +12602,22 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5081</v>
+        <v>0.3705</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-103</v>
+        <v>170</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 37.0% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12668,22 +12668,22 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4919</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>103</v>
+        <v>-170</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-102</v>
+        <v>186</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12724,32 +12724,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3705</v>
+        <v>0.4346</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12790,32 +12790,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.5654</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-170</v>
+        <v>-130</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>168</v>
+        <v>-127</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12866,22 +12866,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4397</v>
+        <v>0.5026</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>127</v>
+        <v>-101</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12932,22 +12932,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5603</v>
+        <v>0.4147999999999999</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-127</v>
+        <v>141</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-122</v>
+        <v>106</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12998,22 +12998,22 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5762</v>
+        <v>0.4244</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-136</v>
+        <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13064,22 +13064,22 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4238</v>
+        <v>0.5756</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>136</v>
+        <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>106</v>
+        <v>-117</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13120,32 +13120,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4244</v>
+        <v>0.3955</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13186,32 +13186,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5756</v>
+        <v>0.6045</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-136</v>
+        <v>-153</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-120</v>
+        <v>-163</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13262,22 +13262,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4239000000000001</v>
+        <v>0.4428</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13328,22 +13328,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5571999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-136</v>
+        <v>-126</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-138</v>
+        <v>122</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13394,22 +13394,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>New York Mets -1.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.437</v>
+        <v>0.4163</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13460,22 +13460,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5837</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-129</v>
+        <v>-140</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>110</v>
+        <v>-133</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -13526,22 +13526,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>New York Mets -1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3941</v>
+        <v>0.4701</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -13592,22 +13592,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6059</v>
+        <v>0.5299</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-154</v>
+        <v>-113</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-155</v>
+        <v>-133</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13658,22 +13658,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4969</v>
+        <v>0.47365</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13724,22 +13724,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5031</v>
+        <v>0.52635</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-101</v>
+        <v>-111</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-113</v>
+        <v>106</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13780,32 +13780,32 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Cincinnati Reds -1.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4198</v>
+        <v>0.295</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 29.5% (fair +239). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13846,32 +13846,32 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5802</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-138</v>
+        <v>-239</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-122</v>
+        <v>-114</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13922,22 +13922,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5058</v>
+        <v>0.4238</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-102</v>
+        <v>136</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13988,22 +13988,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4942</v>
+        <v>0.5762</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>102</v>
+        <v>-136</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14054,22 +14054,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4481</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>123</v>
+        <v>-118</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14120,22 +14120,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5519000000000001</v>
+        <v>0.4582000000000001</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-123</v>
+        <v>118</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-126</v>
+        <v>107</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -14186,21 +14186,23 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4473</v>
+        <v>0.4522</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>124</v>
-      </c>
-      <c r="H59" s="15" t="n"/>
+        <v>121</v>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>170</v>
+      </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
         <v/>
@@ -14223,7 +14225,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14240,7 +14242,7 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
@@ -14250,21 +14252,23 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5527</v>
+        <v>0.5478000000000001</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-124</v>
-      </c>
-      <c r="H60" s="15" t="n"/>
+        <v>-121</v>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-132</v>
+      </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
         <v/>
@@ -14287,7 +14291,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14314,23 +14318,21 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4776</v>
+        <v>0.4473</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>109</v>
-      </c>
-      <c r="H61" s="15" t="n">
-        <v>113</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -14353,7 +14355,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14380,23 +14382,21 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5224</v>
+        <v>0.5527</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-109</v>
-      </c>
-      <c r="H62" s="15" t="n">
-        <v>105</v>
-      </c>
+        <v>-124</v>
+      </c>
+      <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14436,33 +14436,31 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4024</v>
+        <v>0.5737</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>178</v>
-      </c>
+        <v>-135</v>
+      </c>
+      <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
         <v/>
@@ -14485,7 +14483,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14502,33 +14500,31 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5976</v>
+        <v>0.4263</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-149</v>
-      </c>
-      <c r="H64" s="15" t="n">
-        <v>178</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
         <v/>
@@ -14551,7 +14547,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14568,12 +14564,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -14583,14 +14579,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.4587</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-136</v>
+        <v>118</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14615,7 +14611,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14632,12 +14628,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -14647,14 +14643,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.4239</v>
+        <v>0.5413</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>136</v>
+        <v>-118</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14679,7 +14675,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14696,12 +14692,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -14711,14 +14707,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>118</v>
+        <v>-100</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14743,7 +14739,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14760,12 +14756,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -14775,14 +14771,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.4995</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-118</v>
+        <v>100</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14807,7 +14803,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14824,7 +14820,7 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -14839,14 +14835,14 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4201</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-101</v>
+        <v>138</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14871,7 +14867,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14888,7 +14884,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
@@ -14903,14 +14899,14 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4985</v>
+        <v>0.5799</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>101</v>
+        <v>-138</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14935,7 +14931,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14947,17 +14943,17 @@
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -14967,16 +14963,18 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4201</v>
+        <v>0.4559</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>138</v>
-      </c>
-      <c r="H71" s="15" t="n"/>
+        <v>119</v>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
         <v/>
@@ -14999,7 +14997,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15011,17 +15009,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -15031,16 +15029,18 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5799</v>
+        <v>0.5441</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-138</v>
-      </c>
-      <c r="H72" s="15" t="n"/>
+        <v>-119</v>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-113</v>
+      </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
         <v/>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15080,12 +15080,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -15095,17 +15095,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4559</v>
+        <v>0.4318</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15146,12 +15146,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -15161,17 +15161,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5441</v>
+        <v>0.5682</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-119</v>
+        <v>-132</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-113</v>
+        <v>-138</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -15227,17 +15227,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4352</v>
+        <v>0.4356</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>130</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
@@ -15293,11 +15293,11 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5648</v>
+        <v>0.5644</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>-130</v>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4356</v>
+        <v>0.4801</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +130). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15410,12 +15410,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -15425,17 +15425,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5644</v>
+        <v>0.5199</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-130</v>
+        <v>-108</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -130). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15476,12 +15476,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.477</v>
+        <v>0.4457960000000001</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -15557,17 +15557,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.523</v>
+        <v>0.5542039999999999</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-110</v>
+        <v>-124</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15608,12 +15608,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -15623,17 +15623,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4457960000000001</v>
+        <v>0.4644</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15674,12 +15674,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -15689,17 +15689,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5542039999999999</v>
+        <v>0.5356</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-124</v>
+        <v>-115</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15740,12 +15740,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15755,17 +15755,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4714</v>
+        <v>0.4202</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15806,12 +15806,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15821,17 +15821,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5286</v>
+        <v>0.5798</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-112</v>
+        <v>-138</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-113</v>
+        <v>-138</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -15887,17 +15887,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4175</v>
+        <v>0.4991</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>144</v>
+        <v>-108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +140). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
@@ -15953,17 +15953,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5825</v>
+        <v>0.5009</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-140</v>
+        <v>-100</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-138</v>
+        <v>113</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -140). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16004,12 +16004,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -16019,17 +16019,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4992</v>
+        <v>0.7108</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>100</v>
+        <v>-246</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16053,7 +16053,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 71.1% (fair -246). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16070,12 +16070,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -16085,17 +16085,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5008</v>
+        <v>0.2892</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-100</v>
+        <v>246</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 28.9% (fair +246). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16155,10 +16155,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5159</v>
+        <v>0.5263</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-107</v>
+        <v>-111</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>-122</v>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16221,10 +16221,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4841</v>
+        <v>0.4737</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>122</v>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16415,10 +16415,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.442</v>
+        <v>0.4442</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="13">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16479,10 +16479,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5558</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H94" s="15" t="n"/>
       <c r="I94" s="13">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4621</v>
+        <v>0.4615</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16607,10 +16607,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5379</v>
+        <v>0.5385</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16812,13 +16812,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.698</v>
+        <v>0.7083999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-231</v>
+        <v>-243</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-255</v>
+        <v>-285</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.8% (fair -231). Your call.</t>
+          <t>Model 70.8% (fair -243). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16878,13 +16878,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.302</v>
+        <v>0.2916</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 30.2% (fair +231). Your call.</t>
+          <t>Model 29.2% (fair +243). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16940,17 +16940,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>Over 167</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6203768148334138</v>
+        <v>0.6534700194739194</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-163</v>
+        <v>-189</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 65.3% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -17006,17 +17006,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 168.5</t>
+          <t>Under 167</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3796231851665862</v>
+        <v>0.3248299805260806</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 32.5% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -17072,17 +17072,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo +6.5</t>
+          <t>Toronto Tempo +7.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5610150794687777</v>
+        <v>0.5918410726948711</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-128</v>
+        <v>-145</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -17138,17 +17138,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -6.5</t>
+          <t>Golden State Valkyries -7.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4389849205312223</v>
+        <v>0.4081589273051289</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -17208,13 +17208,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.74107</v>
+        <v>0.7299</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-286</v>
+        <v>-270</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-270</v>
+        <v>-257</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 74.1% (fair -286). Your call.</t>
+          <t>Model 73.0% (fair -270). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -17274,13 +17274,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.25893</v>
+        <v>0.2701</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>345</v>
+        <v>255</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 25.9% (fair +286). Your call.</t>
+          <t>Model 27.0% (fair +270). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -17336,17 +17336,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>Over 168</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.53725850755538</v>
+        <v>0.5489231605870841</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-116</v>
+        <v>-122</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -17402,17 +17402,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 168.5</t>
+          <t>Under 168</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.46274149244462</v>
+        <v>0.4277768394129159</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -17436,7 +17436,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -17544,7 +17544,7 @@
         <v>-400</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -17604,13 +17604,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.716</v>
+        <v>0.7214</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-252</v>
+        <v>-259</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-225</v>
+        <v>-236</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 71.6% (fair -252). Your call.</t>
+          <t>Model 72.1% (fair -259). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17670,13 +17670,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.284</v>
+        <v>0.2786</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17700,7 +17700,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 28.4% (fair +252). Your call.</t>
+          <t>Model 27.9% (fair +259). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17732,17 +17732,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 184.5</t>
+          <t>Over 183.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5199</v>
+        <v>0.5261</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -17798,17 +17798,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 184.5</t>
+          <t>Under 183.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4801</v>
+        <v>0.4739</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -18132,10 +18132,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.5273</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>-105</v>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4733000000000001</v>
+        <v>0.4727</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -18264,13 +18264,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4715</v>
+        <v>0.4739</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -18294,7 +18294,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -18330,13 +18330,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5285</v>
+        <v>0.5261</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -18396,13 +18396,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6715</v>
+        <v>0.6665</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-204</v>
+        <v>-200</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 67.2% (fair -204). Your call.</t>
+          <t>Model 66.6% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -18462,13 +18462,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.3285</v>
+        <v>0.3335</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -18492,7 +18492,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 32.9% (fair +204). Your call.</t>
+          <t>Model 33.4% (fair +200). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -18792,13 +18792,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.7567</v>
+        <v>0.7513</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-311</v>
+        <v>-302</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-355</v>
+        <v>-317</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 75.7% (fair -311). Your call.</t>
+          <t>Model 75.1% (fair -302). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.2433</v>
+        <v>0.2487</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 24.3% (fair +311). Your call.</t>
+          <t>Model 24.9% (fair +302). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -18924,10 +18924,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.5446</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>-108</v>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -18990,13 +18990,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4578</v>
+        <v>0.4554</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -19052,17 +19052,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire +9.5</t>
+          <t>Portland Fire +7.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5501278048239971</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-105</v>
+        <v>122</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -19118,17 +19118,17 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -9.5</t>
+          <t>Las Vegas Aces -7.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4436</v>
+        <v>0.4498721951760029</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>

--- a/data/output/workbook/2026-07-08.xlsx
+++ b/data/output/workbook/2026-07-08.xlsx
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="11106150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="11182350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 14:26</t>
+          <t>2026-07-08 15:48</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,244 +1175,167 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Athletics offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D71" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E71" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F71" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G71" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H71" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I71" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J71" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K71" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L71" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M71" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N71" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O71" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P71" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q71" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.687</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>3.949</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.146000000000001</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.687</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>3.5</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.592</v>
+        <v>3.949</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.062</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -1471,25 +1394,25 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.898</v>
+        <v>7.592</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.625</v>
+        <v>1.062</v>
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
@@ -1548,321 +1471,321 @@
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>7.776</v>
+        <v>0.898</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
+      <c r="B76" s="32" t="n">
         <v>0.608</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C76" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D76" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E76" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F76" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G76" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="33" t="inlineStr">
+      <c r="H76" s="33" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="36" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K76" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L76" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M76" s="32" t="n">
         <v>0.133</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N76" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O76" s="32" t="n">
         <v>0.233</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P76" s="32" t="n">
         <v>0.346</v>
       </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Athletics defense</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B78" s="30" t="inlineStr">
+      <c r="B79" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C78" s="30" t="inlineStr">
+      <c r="C79" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D78" s="30" t="inlineStr">
+      <c r="D79" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="E79" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F78" s="30" t="inlineStr">
+      <c r="F79" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G78" s="30" t="inlineStr">
+      <c r="G79" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H78" s="30" t="inlineStr">
+      <c r="H79" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I78" s="30" t="inlineStr">
+      <c r="I79" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J78" s="30" t="inlineStr">
+      <c r="J79" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K78" s="30" t="inlineStr">
+      <c r="K79" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L78" s="30" t="inlineStr">
+      <c r="L79" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M78" s="30" t="inlineStr">
+      <c r="M79" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N78" s="30" t="inlineStr">
+      <c r="N79" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O78" s="30" t="inlineStr">
+      <c r="O79" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P78" s="30" t="inlineStr">
+      <c r="P79" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q78" s="30" t="inlineStr">
+      <c r="Q79" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>6.767</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>5.289</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.755</v>
+        <v>4.333</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.067</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>6.133</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>6.767</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>5.289</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.02</v>
+        <v>7.755</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -1921,25 +1844,25 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.271</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C82" s="32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D82" s="32" t="inlineStr">
         <is>
@@ -1998,72 +1921,149 @@
         </is>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>1.271</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C83" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="32" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B83" s="32" t="n">
+      <c r="B84" s="32" t="n">
         <v>0.577</v>
       </c>
-      <c r="C83" s="32" t="n">
+      <c r="C84" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="D83" s="32" t="n">
+      <c r="D84" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E83" s="32" t="n">
+      <c r="E84" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F83" s="32" t="n">
+      <c r="F84" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G83" s="32" t="n">
+      <c r="G84" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I83" s="32" t="inlineStr">
+      <c r="I84" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J83" s="33" t="inlineStr">
+      <c r="J84" s="33" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="K83" s="32" t="n">
+      <c r="K84" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="L83" s="32" t="n">
+      <c r="L84" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M83" s="32" t="n">
+      <c r="M84" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N83" s="32" t="n">
+      <c r="N84" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O83" s="32" t="n">
+      <c r="O84" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P83" s="32" t="n">
+      <c r="P84" s="32" t="n">
         <v>0.734</v>
       </c>
-      <c r="Q83" s="34" t="inlineStr">
+      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2082,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,328 +2099,174 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="30" t="inlineStr">
+      <c r="J72" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K72" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
+      <c r="L72" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="30" t="inlineStr">
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="30" t="inlineStr">
+      <c r="N72" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="30" t="inlineStr">
+      <c r="O72" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="30" t="inlineStr">
+      <c r="P72" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="30" t="inlineStr">
+      <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>4.975</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.762</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.958</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.333</v>
+        <v>4.975</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.167</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>5.3</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.896</v>
+        <v>4.762</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>7.688</v>
+        <v>8.958</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D74" s="32" t="inlineStr">
         <is>
@@ -2479,396 +2325,396 @@
         </is>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.292</v>
+        <v>7.792</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>9.292</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
+      <c r="B77" s="32" t="n">
         <v>0.61</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="32" t="n">
+      <c r="G77" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H75" s="36" t="inlineStr">
+      <c r="H77" s="36" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J75" s="35" t="inlineStr">
+      <c r="J77" s="35" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K75" s="32" t="n">
+      <c r="K77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L75" s="32" t="n">
+      <c r="L77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M75" s="32" t="n">
+      <c r="M77" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N75" s="32" t="n">
+      <c r="N77" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O75" s="32" t="n">
+      <c r="O77" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P75" s="32" t="n">
+      <c r="P77" s="32" t="n">
         <v>0.418</v>
       </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B78" s="30" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C78" s="30" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D78" s="30" t="inlineStr">
+      <c r="D80" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F78" s="30" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G78" s="30" t="inlineStr">
+      <c r="G80" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H78" s="30" t="inlineStr">
+      <c r="H80" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I78" s="30" t="inlineStr">
+      <c r="I80" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J78" s="30" t="inlineStr">
+      <c r="J80" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K78" s="30" t="inlineStr">
+      <c r="K80" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L78" s="30" t="inlineStr">
+      <c r="L80" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M78" s="30" t="inlineStr">
+      <c r="M80" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N78" s="30" t="inlineStr">
+      <c r="N80" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O78" s="30" t="inlineStr">
+      <c r="O80" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P78" s="30" t="inlineStr">
+      <c r="P80" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q78" s="30" t="inlineStr">
+      <c r="Q80" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>5.238</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>4.025</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>7.312</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.238</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>5.5</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.062</v>
+        <v>4.025</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>9.708</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
@@ -2930,72 +2776,226 @@
         <v>9</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.561999999999999</v>
+        <v>7.312</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="n">
+        <v>9.708</v>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="32" t="inlineStr"/>
+      <c r="J84" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P84" s="32" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q84" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B83" s="32" t="n">
+      <c r="B85" s="32" t="n">
         <v>0.582</v>
       </c>
-      <c r="C83" s="32" t="n">
+      <c r="C85" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D83" s="32" t="n">
+      <c r="D85" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E83" s="32" t="n">
+      <c r="E85" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F83" s="32" t="n">
+      <c r="F85" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G83" s="32" t="n">
+      <c r="G85" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="36" t="inlineStr">
+      <c r="H85" s="36" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I83" s="32" t="inlineStr">
+      <c r="I85" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J83" s="33" t="inlineStr">
+      <c r="J85" s="33" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K83" s="32" t="n">
+      <c r="K85" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="L83" s="32" t="n">
+      <c r="L85" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M83" s="32" t="n">
+      <c r="M85" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N83" s="32" t="n">
+      <c r="N85" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="O83" s="32" t="n">
+      <c r="O85" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P83" s="32" t="n">
+      <c r="P85" s="32" t="n">
         <v>0.597</v>
       </c>
-      <c r="Q83" s="34" t="inlineStr">
+      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-170</v>
+        <v>-167</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.621</v>
+        <v>0.6517999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-164</v>
+        <v>-187</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8968,17 +8968,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5515</v>
+        <v>0.6382</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-123</v>
+        <v>-176</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9014,17 +9014,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9034,17 +9034,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5593</v>
+        <v>0.621</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-127</v>
+        <v>-164</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9085,12 +9085,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9100,17 +9100,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies +1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.7025</v>
+        <v>0.5766</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-236</v>
+        <v>-136</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-112</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 70.2% (fair -236). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6135999999999999</v>
+        <v>0.5515</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-159</v>
+        <v>-123</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9212,7 +9212,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9227,22 +9227,22 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7269</v>
+        <v>0.706</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-266</v>
+        <v>-240</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-138</v>
+        <v>-112</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 72.7% (fair -266). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9283,12 +9283,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9298,17 +9298,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4485</v>
+        <v>0.6119</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>123</v>
+        <v>-158</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9344,37 +9344,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries @ Toronto Tempo</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7308</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-141</v>
+        <v>-271</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>-138</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 73.1% (fair -271). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9410,37 +9410,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.2086</v>
+        <v>0.4485</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>379</v>
+        <v>123</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>471</v>
+        <v>178</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 20.9% (fair +379). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9476,37 +9476,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6502</v>
+        <v>0.2073</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-186</v>
+        <v>382</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-125</v>
+        <v>488</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 20.7% (fair +382). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9547,32 +9547,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Golden State Valkyries @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4407</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>127</v>
+        <v>-141</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 58.4% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9632,13 +9632,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.2868</v>
+        <v>0.2856</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 28.7% (fair +249). Your call.</t>
+          <t>Model 28.6% (fair +250). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9694,17 +9694,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4498</v>
+        <v>0.4234</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9811,32 +9811,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Connecticut Sun</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.4232</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-111</v>
+        <v>136</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9872,37 +9872,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Seattle Storm +10.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4659</v>
+        <v>0.5206</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>115</v>
+        <v>-109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4232</v>
+        <v>0.4331</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10009,32 +10009,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Indiana Fever @ Los Angeles Sparks</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 184</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5129</v>
+        <v>0.4685</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-105</v>
+        <v>113</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10070,37 +10070,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 175.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5472</v>
+        <v>0.485</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-121</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10136,37 +10136,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Las Vegas Aces @ Portland Fire</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5693</v>
+        <v>0.5472</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-132</v>
+        <v>-121</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10207,32 +10207,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5768</v>
+        <v>0.5641</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>-129</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-117</v>
+        <v>-111</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10268,37 +10268,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.501</v>
+        <v>0.5768</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-100</v>
+        <v>-136</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>-117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10339,32 +10339,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4916</v>
+        <v>0.374</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10400,12 +10400,12 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.501</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-124</v>
+        <v>-100</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10487,7 +10487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5084</v>
+        <v>0.515</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-103</v>
+        <v>-106</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10697,13 +10697,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4916</v>
+        <v>0.485</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.46545</v>
+        <v>0.465</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>115</v>
@@ -10829,13 +10829,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5345500000000001</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>-115</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.44105</v>
+        <v>0.47625</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>116</v>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11093,13 +11093,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5589500000000001</v>
+        <v>0.5237499999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3498</v>
+        <v>0.3618</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11225,13 +11225,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6502</v>
+        <v>0.6382</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-186</v>
+        <v>-176</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-125</v>
+        <v>150</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11291,10 +11291,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4119</v>
+        <v>0.4343</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>127</v>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5881</v>
+        <v>0.5657</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-143</v>
+        <v>-130</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5461</v>
+        <v>0.58495</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-120</v>
+        <v>-141</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11489,13 +11489,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4539</v>
+        <v>0.41505</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11555,13 +11555,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4498</v>
+        <v>0.4331</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5502</v>
+        <v>0.5669</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-122</v>
+        <v>-131</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-114</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11687,10 +11687,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4472</v>
+        <v>0.4594</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>108</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11753,10 +11753,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.5406</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-124</v>
+        <v>-118</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-108</v>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11819,10 +11819,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.55175</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-118</v>
+        <v>-123</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>109</v>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11885,13 +11885,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4585</v>
+        <v>0.44825</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11951,10 +11951,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4407</v>
+        <v>0.4234</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>165</v>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12017,10 +12017,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5593</v>
+        <v>0.5766</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-127</v>
+        <v>-136</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>170</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5097</v>
+        <v>0.5106999999999999</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>-104</v>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4903</v>
+        <v>0.4893</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>104</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12211,17 +12211,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.46995</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-111</v>
+        <v>113</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12277,17 +12277,17 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4733000000000001</v>
+        <v>0.44285</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12347,10 +12347,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.4663</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>108</v>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12413,10 +12413,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5337</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>-108</v>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12475,17 +12475,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4479</v>
+        <v>0.5498</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>123</v>
+        <v>-122</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12541,17 +12541,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.46</v>
+        <v>0.4502</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12611,10 +12611,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3705</v>
+        <v>0.374</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>186</v>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12677,10 +12677,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-170</v>
+        <v>-167</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>186</v>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4368</v>
+        <v>0.4346</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5632</v>
+        <v>0.5654</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-127</v>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12871,17 +12871,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4808</v>
+        <v>0.501</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>108</v>
+        <v>-100</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-102</v>
+        <v>127</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12937,14 +12937,14 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4366</v>
+        <v>0.499</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>108</v>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.396</v>
+        <v>0.3956</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>153</v>
@@ -13205,13 +13205,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.604</v>
+        <v>0.6044</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>-153</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.42975</v>
+        <v>0.42785</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>117</v>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13337,10 +13337,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5702499999999999</v>
+        <v>0.5721499999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-133</v>
+        <v>-134</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>115</v>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3864</v>
+        <v>0.3881</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>130</v>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13469,10 +13469,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6135999999999999</v>
+        <v>0.6119</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-159</v>
+        <v>-158</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>112</v>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13535,13 +13535,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4659</v>
+        <v>0.4685</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5341</v>
+        <v>0.5315</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>-133</v>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13667,13 +13667,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4394</v>
+        <v>0.44275</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13733,13 +13733,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5606</v>
+        <v>0.55725</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-128</v>
+        <v>-126</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.2975</v>
+        <v>0.294</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>156</v>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 29.8% (fair +236). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.7025</v>
+        <v>0.706</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-236</v>
+        <v>-240</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-112</v>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 70.2% (fair -236). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13931,13 +13931,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4307</v>
+        <v>0.4359</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13997,13 +13997,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5693</v>
+        <v>0.5641</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-132</v>
+        <v>-129</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5014</v>
+        <v>0.5246</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-101</v>
+        <v>-110</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>108</v>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14129,13 +14129,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4986</v>
+        <v>0.4754</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-101</v>
+        <v>127</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4567</v>
+        <v>0.4525</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14391,10 +14391,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5433</v>
+        <v>0.5475</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4202</v>
+        <v>0.4201</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>138</v>
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5798</v>
+        <v>0.5799</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>-138</v>
@@ -15095,17 +15095,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4596</v>
+        <v>0.46645</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-105</v>
+        <v>127</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15161,14 +15161,14 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.53355</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>120</v>
+        <v>-114</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>110</v>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15231,13 +15231,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.6171</v>
+        <v>0.6198</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-161</v>
+        <v>-163</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-155</v>
+        <v>-165</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15297,10 +15297,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.3829</v>
+        <v>0.3802</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>140</v>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15363,10 +15363,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4311</v>
+        <v>0.4286</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>133</v>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15429,13 +15429,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5689</v>
+        <v>0.5714</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15491,17 +15491,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.445</v>
+        <v>0.4233</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-105</v>
+        <v>117</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15557,17 +15557,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4683999999999999</v>
+        <v>0.5767</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>113</v>
+        <v>-136</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +113). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4833</v>
+        <v>0.5039</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>107</v>
+        <v>-102</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5167</v>
+        <v>0.4961</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-107</v>
+        <v>102</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16023,13 +16023,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4531</v>
+        <v>0.4572</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16053,7 +16053,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16089,13 +16089,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4602999999999999</v>
+        <v>0.4561999999999999</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16155,13 +16155,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.6115</v>
+        <v>0.5946</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-157</v>
+        <v>-147</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-170</v>
+        <v>-144</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -157). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16221,13 +16221,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3885</v>
+        <v>0.4054</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +157). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16419,13 +16419,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4671</v>
+        <v>0.44635</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16485,13 +16485,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5328999999999999</v>
+        <v>0.55365</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-114</v>
+        <v>-124</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-120</v>
+        <v>-105</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16557,7 +16557,7 @@
         <v>164</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16623,7 +16623,7 @@
         <v>-164</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16683,13 +16683,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4644</v>
+        <v>0.4614</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5356</v>
+        <v>0.5386</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>-113</v>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16815,13 +16815,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4838</v>
+        <v>0.484</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>107</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16881,13 +16881,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5162</v>
+        <v>0.516</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>-107</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16943,17 +16943,17 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.6099</v>
+        <v>0.3482</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>-156</v>
+        <v>187</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>-180</v>
+        <v>162</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17009,17 +17009,17 @@
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.3901</v>
+        <v>0.6517999999999999</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>156</v>
+        <v>-187</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17207,17 +17207,17 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5471</v>
+        <v>0.4912</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-121</v>
+        <v>104</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17273,17 +17273,17 @@
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4529</v>
+        <v>0.4228999999999999</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.42</v>
+        <v>0.3956</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17409,13 +17409,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.6044</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-138</v>
+        <v>-153</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-145</v>
+        <v>-155</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17607,10 +17607,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.7269</v>
+        <v>0.7308</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-266</v>
+        <v>-271</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>-138</v>
@@ -17637,7 +17637,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 72.7% (fair -266). Your call.</t>
+          <t>Model 73.1% (fair -271). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17673,13 +17673,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 27.3% (fair +266). Your call.</t>
+          <t>Model 26.9% (fair +271). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4872</v>
+        <v>0.4717</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-110</v>
+        <v>117</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17801,17 +17801,17 @@
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4271999999999999</v>
+        <v>0.5283</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>134</v>
+        <v>-112</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17871,13 +17871,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4717</v>
+        <v>0.4641</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17937,13 +17937,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5359</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.526</v>
+        <v>0.5263</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>-111</v>
@@ -18069,7 +18069,7 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.474</v>
+        <v>0.4737</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>111</v>
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5012</v>
+        <v>0.4917</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-100</v>
+        <v>103</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>-105</v>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18201,10 +18201,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4988</v>
+        <v>0.5083</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>100</v>
+        <v>-103</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-115</v>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5854</v>
+        <v>0.585</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>-141</v>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4146</v>
+        <v>0.415</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>141</v>
@@ -18508,31 +18508,33 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4377</v>
+        <v>0.5149</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>128</v>
-      </c>
-      <c r="H125" s="15" t="n"/>
+        <v>-106</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
         <v/>
@@ -18555,7 +18557,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18572,31 +18574,33 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5623</v>
+        <v>0.4851</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H126" s="15" t="n"/>
+        <v>106</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-104</v>
+      </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
         <v/>
@@ -18619,7 +18623,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18636,31 +18640,33 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4647</v>
+        <v>0.3664</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="H127" s="15" t="n"/>
+        <v>173</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>162</v>
+      </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
         <v/>
@@ -18683,7 +18689,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 36.6% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18700,31 +18706,33 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ San Francisco Giants</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5353</v>
+        <v>0.6335999999999999</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H128" s="15" t="n"/>
+        <v>-173</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-170</v>
+      </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
         <v/>
@@ -18747,7 +18755,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18756,9 +18764,529 @@
         <v/>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="H129" s="15" t="n"/>
+      <c r="I129" s="13">
+        <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
+        <v/>
+      </c>
+      <c r="J129" s="16">
+        <f>IF($H$129="","",$F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))</f>
+        <v/>
+      </c>
+      <c r="K129" s="17">
+        <f>IF($H$129="","",MAX(0,($F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))/IF($H$129&lt;0,-100/$H$129,$H$129/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L129" s="18">
+        <f>IF($H$129="","",ROUND(MIN($K$129,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M129" s="12">
+        <f>IF($J$129="","",IF($J$129&lt;0,"Pass",IF($J$129&lt;'Settings'!$B$4,"Thin",IF($J$129&lt;0.06,"✅ Sharp band",IF($J$129&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N129" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.8% (fair +128). Your call.</t>
+        </is>
+      </c>
+      <c r="O129" s="15" t="n"/>
+      <c r="P129" s="16">
+        <f>IF(OR($H$129="",$O$129=""),"",(1+IF($H$129&lt;0,-100/$H$129,$H$129/100))/(1+IF($O$129&lt;0,-100/$O$129,$O$129/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>0.5623</v>
+      </c>
+      <c r="G130" s="14" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H130" s="15" t="n"/>
+      <c r="I130" s="13">
+        <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
+        <v/>
+      </c>
+      <c r="J130" s="16">
+        <f>IF($H$130="","",$F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))</f>
+        <v/>
+      </c>
+      <c r="K130" s="17">
+        <f>IF($H$130="","",MAX(0,($F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))/IF($H$130&lt;0,-100/$H$130,$H$130/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L130" s="18">
+        <f>IF($H$130="","",ROUND(MIN($K$130,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M130" s="12">
+        <f>IF($J$130="","",IF($J$130&lt;0,"Pass",IF($J$130&lt;'Settings'!$B$4,"Thin",IF($J$130&lt;0.06,"✅ Sharp band",IF($J$130&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N130" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.2% (fair -128). Your call.</t>
+        </is>
+      </c>
+      <c r="O130" s="15" t="n"/>
+      <c r="P130" s="16">
+        <f>IF(OR($H$130="",$O$130=""),"",(1+IF($H$130&lt;0,-100/$H$130,$H$130/100))/(1+IF($O$130&lt;0,-100/$O$130,$O$130/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I131" s="13">
+        <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
+        <v/>
+      </c>
+      <c r="J131" s="16">
+        <f>IF($H$131="","",$F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))</f>
+        <v/>
+      </c>
+      <c r="K131" s="17">
+        <f>IF($H$131="","",MAX(0,($F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))/IF($H$131&lt;0,-100/$H$131,$H$131/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L131" s="18">
+        <f>IF($H$131="","",ROUND(MIN($K$131,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M131" s="12">
+        <f>IF($J$131="","",IF($J$131&lt;0,"Pass",IF($J$131&lt;'Settings'!$B$4,"Thin",IF($J$131&lt;0.06,"✅ Sharp band",IF($J$131&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N131" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.7% (fair -107). Your call.</t>
+        </is>
+      </c>
+      <c r="O131" s="15" t="n"/>
+      <c r="P131" s="16">
+        <f>IF(OR($H$131="",$O$131=""),"",(1+IF($H$131&lt;0,-100/$H$131,$H$131/100))/(1+IF($O$131&lt;0,-100/$O$131,$O$131/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="G132" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I132" s="13">
+        <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>IF($H$132="","",$F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))</f>
+        <v/>
+      </c>
+      <c r="K132" s="17">
+        <f>IF($H$132="","",MAX(0,($F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))/IF($H$132&lt;0,-100/$H$132,$H$132/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L132" s="18">
+        <f>IF($H$132="","",ROUND(MIN($K$132,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M132" s="12">
+        <f>IF($J$132="","",IF($J$132&lt;0,"Pass",IF($J$132&lt;'Settings'!$B$4,"Thin",IF($J$132&lt;0.06,"✅ Sharp band",IF($J$132&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N132" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.3% (fair +107). Your call.</t>
+        </is>
+      </c>
+      <c r="O132" s="15" t="n"/>
+      <c r="P132" s="16">
+        <f>IF(OR($H$132="",$O$132=""),"",(1+IF($H$132&lt;0,-100/$H$132,$H$132/100))/(1+IF($O$132&lt;0,-100/$O$132,$O$132/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres -1.5</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="G133" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>168</v>
+      </c>
+      <c r="I133" s="13">
+        <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
+        <v/>
+      </c>
+      <c r="J133" s="16">
+        <f>IF($H$133="","",$F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))</f>
+        <v/>
+      </c>
+      <c r="K133" s="17">
+        <f>IF($H$133="","",MAX(0,($F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))/IF($H$133&lt;0,-100/$H$133,$H$133/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L133" s="18">
+        <f>IF($H$133="","",ROUND(MIN($K$133,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M133" s="12">
+        <f>IF($J$133="","",IF($J$133&lt;0,"Pass",IF($J$133&lt;'Settings'!$B$4,"Thin",IF($J$133&lt;0.06,"✅ Sharp band",IF($J$133&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N133" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.0% (fair +163). Your call.</t>
+        </is>
+      </c>
+      <c r="O133" s="15" t="n"/>
+      <c r="P133" s="16">
+        <f>IF(OR($H$133="",$O$133=""),"",(1+IF($H$133&lt;0,-100/$H$133,$H$133/100))/(1+IF($O$133&lt;0,-100/$O$133,$O$133/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks +1.5</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>0.6194999999999999</v>
+      </c>
+      <c r="G134" s="14" t="n">
+        <v>-163</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>-185</v>
+      </c>
+      <c r="I134" s="13">
+        <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
+        <v/>
+      </c>
+      <c r="J134" s="16">
+        <f>IF($H$134="","",$F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))</f>
+        <v/>
+      </c>
+      <c r="K134" s="17">
+        <f>IF($H$134="","",MAX(0,($F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))/IF($H$134&lt;0,-100/$H$134,$H$134/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L134" s="18">
+        <f>IF($H$134="","",ROUND(MIN($K$134,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M134" s="12">
+        <f>IF($J$134="","",IF($J$134&lt;0,"Pass",IF($J$134&lt;'Settings'!$B$4,"Thin",IF($J$134&lt;0.06,"✅ Sharp band",IF($J$134&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N134" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.9% (fair -163). Your call.</t>
+        </is>
+      </c>
+      <c r="O134" s="15" t="n"/>
+      <c r="P134" s="16">
+        <f>IF(OR($H$134="",$O$134=""),"",(1+IF($H$134&lt;0,-100/$H$134,$H$134/100))/(1+IF($O$134&lt;0,-100/$O$134,$O$134/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="G135" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="13">
+        <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
+        <v/>
+      </c>
+      <c r="J135" s="16">
+        <f>IF($H$135="","",$F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))</f>
+        <v/>
+      </c>
+      <c r="K135" s="17">
+        <f>IF($H$135="","",MAX(0,($F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))/IF($H$135&lt;0,-100/$H$135,$H$135/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L135" s="18">
+        <f>IF($H$135="","",ROUND(MIN($K$135,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M135" s="12">
+        <f>IF($J$135="","",IF($J$135&lt;0,"Pass",IF($J$135&lt;'Settings'!$B$4,"Thin",IF($J$135&lt;0.06,"✅ Sharp band",IF($J$135&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N135" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.5% (fair +115). Your call.</t>
+        </is>
+      </c>
+      <c r="O135" s="15" t="n"/>
+      <c r="P135" s="16">
+        <f>IF(OR($H$135="",$O$135=""),"",(1+IF($H$135&lt;0,-100/$H$135,$H$135/100))/(1+IF($O$135&lt;0,-100/$O$135,$O$135/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="G136" s="14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="13">
+        <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
+        <v/>
+      </c>
+      <c r="J136" s="16">
+        <f>IF($H$136="","",$F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))</f>
+        <v/>
+      </c>
+      <c r="K136" s="17">
+        <f>IF($H$136="","",MAX(0,($F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))/IF($H$136&lt;0,-100/$H$136,$H$136/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L136" s="18">
+        <f>IF($H$136="","",ROUND(MIN($K$136,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M136" s="12">
+        <f>IF($J$136="","",IF($J$136&lt;0,"Pass",IF($J$136&lt;'Settings'!$B$4,"Thin",IF($J$136&lt;0.06,"✅ Sharp band",IF($J$136&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N136" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.5% (fair -115). Your call.</t>
+        </is>
+      </c>
+      <c r="O136" s="15" t="n"/>
+      <c r="P136" s="16">
+        <f>IF(OR($H$136="",$O$136=""),"",(1+IF($H$136&lt;0,-100/$H$136,$H$136/100))/(1+IF($O$136&lt;0,-100/$O$136,$O$136/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J128">
+  <conditionalFormatting sqref="J5:J136">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -18924,10 +19452,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7132000000000001</v>
+        <v>0.7143999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-249</v>
+        <v>-250</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-300</v>
@@ -18954,7 +19482,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.3% (fair -249). Your call.</t>
+          <t>Model 71.4% (fair -250). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -18990,13 +19518,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2868</v>
+        <v>0.2856</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -19020,7 +19548,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 28.7% (fair +249). Your call.</t>
+          <t>Model 28.6% (fair +250). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19320,13 +19848,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7255</v>
+        <v>0.7246</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-264</v>
+        <v>-263</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-244</v>
+        <v>-237</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19350,7 +19878,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 72.5% (fair -264). Your call.</t>
+          <t>Model 72.5% (fair -263). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19386,10 +19914,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2745</v>
+        <v>0.2754</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>245</v>
@@ -19416,7 +19944,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 27.5% (fair +264). Your call.</t>
+          <t>Model 27.5% (fair +263). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19448,17 +19976,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Over 168.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.53725850755538</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-111</v>
+        <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -19482,7 +20010,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -19514,14 +20042,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 167.5</t>
+          <t>Under 168.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4746</v>
+        <v>0.46274149244462</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -19548,7 +20076,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -19656,7 +20184,7 @@
         <v>-400</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -19716,13 +20244,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7237</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-262</v>
+        <v>-250</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-242</v>
+        <v>-217</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -19746,7 +20274,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 72.4% (fair -262). Your call.</t>
+          <t>Model 71.4% (fair -250). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -19782,13 +20310,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2763</v>
+        <v>0.2858</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -19812,7 +20340,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 27.6% (fair +262). Your call.</t>
+          <t>Model 28.6% (fair +250). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -19844,17 +20372,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 184</t>
+          <t>Over 183.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5129</v>
+        <v>0.5668009120293164</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-105</v>
+        <v>-131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -19878,7 +20406,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -19910,14 +20438,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 184</t>
+          <t>Under 183.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4639</v>
+        <v>0.4331990879706836</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-104</v>
@@ -19944,7 +20472,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -20052,7 +20580,7 @@
         <v>-245</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -20112,13 +20640,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.2086</v>
+        <v>0.2073</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -20142,7 +20670,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 20.9% (fair +379). Your call.</t>
+          <t>Model 20.7% (fair +382). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -20178,13 +20706,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.7914</v>
+        <v>0.7927</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-379</v>
+        <v>-382</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-488</v>
+        <v>-456</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -20208,7 +20736,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 79.1% (fair -379). Your call.</t>
+          <t>Model 79.3% (fair -382). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -20240,17 +20768,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 169.5</t>
+          <t>Over 168.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5273</v>
+        <v>0.5382</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-112</v>
+        <v>-117</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -20274,7 +20802,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -20306,14 +20834,14 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 169.5</t>
+          <t>Under 168.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.4618</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-104</v>
@@ -20340,7 +20868,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -20376,10 +20904,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4745</v>
+        <v>0.4794</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>-105</v>
@@ -20406,7 +20934,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -20442,13 +20970,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5255000000000001</v>
+        <v>0.5206</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-111</v>
+        <v>-109</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -20472,7 +21000,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -22769,7 +23297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22786,246 +23314,167 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>5.203</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5.833</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.438000000000001</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.203</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5.833</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>7th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.2</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.833</v>
+        <v>4.8</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.104</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -23089,22 +23538,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.062</v>
+        <v>8.833</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.458</v>
+        <v>1.104</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -23168,317 +23617,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8</v>
+        <v>1.062</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.462</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.481</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.537</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.747</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.537</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>4.8</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.896</v>
+        <v>4.747</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.271</v>
+        <v>8.208</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -23542,22 +23991,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.354</v>
+        <v>7.896</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.917</v>
+        <v>1.271</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -23621,68 +24070,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.708</v>
+        <v>1.354</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.833</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.436</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-08.xlsx
+++ b/data/output/workbook/2026-07-08.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11182350"/>
+    <ext cx="10125075" cy="10753725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08 15:48</t>
+          <t>2026-07-08 17:18</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,903 +2099,903 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.762</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Atlanta Braves offense vs Pittsburgh Pirates defense</t>
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>8.958</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.975</v>
+        <v>7.688</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>5.3</v>
+        <v>9</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>4.762</v>
+        <v>9.292</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>5.238</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
-        <v>8.958</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="B79" s="32" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.312</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B75" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="C75" s="32" t="n">
+      <c r="B80" s="32" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="P80" s="32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>7.688</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>9.292</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Atlanta Braves defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B80" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C80" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D80" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F80" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G80" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H80" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I80" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J80" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K80" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L80" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M80" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N80" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O80" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P80" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q80" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>5.238</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H81" s="36" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>5.5</v>
+        <v>9.708</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>4.025</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.582</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.8</v>
       </c>
       <c r="O82" s="32" t="n">
-        <v>9</v>
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>7.312</v>
+        <v>0.597</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="C83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B84" s="32" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="32" t="inlineStr"/>
-      <c r="J84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P84" s="32" t="n">
-        <v>8.561999999999999</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B85" s="32" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="C85" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D85" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E85" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F85" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G85" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="36" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I85" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J85" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K85" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M85" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N85" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O85" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P85" s="32" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3946,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3963,167 +3963,246 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.683</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.133</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.683</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>8.109</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>3.4</v>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.397</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -4187,22 +4266,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -4266,313 +4345,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.597</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.778</v>
+        <v>0.487</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.641</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.641</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>8.778</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.5</v>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P77" s="32" t="n">
-        <v>3.854</v>
+        <v>7.609</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -4636,22 +4715,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -4715,147 +4794,68 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.244</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.526</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.5669999999999999</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.435</v>
+        <v>0.506</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6517999999999999</v>
+        <v>0.6223000000000001</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-187</v>
+        <v>-165</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.2% (fair -187). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8948,7 +8948,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -8972,10 +8972,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6382</v>
+        <v>0.6508</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-176</v>
+        <v>-186</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>150</v>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 65.1% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9014,17 +9014,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9034,17 +9034,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.621</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-164</v>
+        <v>-133</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5766</v>
+        <v>0.5781000000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>170</v>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5515</v>
+        <v>0.6976</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-123</v>
+        <v>-231</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>178</v>
+        <v>-113</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 69.8% (fair -231). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9212,7 +9212,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9227,22 +9227,22 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.706</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-240</v>
+        <v>-281</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-112</v>
+        <v>-144</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.6% (fair -240). Your call.</t>
+          <t>Model 73.7% (fair -281). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9278,37 +9278,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6119</v>
+        <v>0.2073</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-158</v>
+        <v>382</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>112</v>
+        <v>488</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 20.7% (fair +382). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9344,37 +9344,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Golden State Valkyries @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.7308</v>
+        <v>0.5848</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-271</v>
+        <v>-141</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-138</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 73.1% (fair -271). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4485</v>
+        <v>0.4299</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>178</v>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9476,37 +9476,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2073</v>
+        <v>0.6319</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>382</v>
+        <v>-172</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>488</v>
+        <v>-118</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 20.7% (fair +382). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9557,22 +9557,22 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.2868</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-141</v>
+        <v>249</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 28.7% (fair +249). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries @ Toronto Tempo</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.2856</v>
+        <v>0.4219</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>250</v>
+        <v>137</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 28.6% (fair +250). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9694,17 +9694,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4234</v>
+        <v>0.4335</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9811,12 +9811,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9826,17 +9826,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4232</v>
+        <v>0.374</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9872,17 +9872,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Atlanta Dream</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9892,17 +9892,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +10.5</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5697</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-109</v>
+        <v>-132</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>-111</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9938,12 +9938,12 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -9953,22 +9953,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.485</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10004,7 +10004,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -10019,22 +10019,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4685</v>
+        <v>0.4957</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10070,37 +10070,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Las Vegas Aces @ Portland Fire</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.485</v>
+        <v>0.5472</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>106</v>
+        <v>-121</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10141,32 +10141,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Portland Fire</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 175.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5472</v>
+        <v>0.5363</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-121</v>
+        <v>-116</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10202,37 +10202,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Seattle Storm @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 168.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5641</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-129</v>
+        <v>-115</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-111</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10273,32 +10273,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5768</v>
+        <v>0.4659</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-136</v>
+        <v>115</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-117</v>
+        <v>130</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10339,32 +10339,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.374</v>
+        <v>0.4865</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +167). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10400,7 +10400,7 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.501</v>
+        <v>0.4903</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-100</v>
+        <v>104</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.515</v>
+        <v>0.5135000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-106</v>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10697,13 +10697,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.485</v>
+        <v>0.4865</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>106</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10769,7 +10769,7 @@
         <v>115</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10835,7 +10835,7 @@
         <v>-115</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10895,13 +10895,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4588</v>
+        <v>0.4547</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10961,10 +10961,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5412</v>
+        <v>0.5453</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-117</v>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11027,13 +11027,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.47625</v>
+        <v>0.4765</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11093,13 +11093,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5237499999999999</v>
+        <v>0.5235000000000001</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-110</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3618</v>
+        <v>0.3681</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 36.2% (fair +176). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11225,13 +11225,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6382</v>
+        <v>0.6319</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-176</v>
+        <v>-172</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>150</v>
+        <v>-118</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11291,10 +11291,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4343</v>
+        <v>0.4332</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>127</v>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5657</v>
+        <v>0.5668</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.58495</v>
+        <v>0.58305</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>113</v>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11489,13 +11489,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.41505</v>
+        <v>0.41695</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11555,13 +11555,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.4303</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11621,13 +11621,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5697</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-114</v>
+        <v>-111</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.457</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11753,10 +11753,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.543</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-108</v>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11819,13 +11819,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.55175</v>
+        <v>0.5447</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11885,13 +11885,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.44825</v>
+        <v>0.4553</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11951,10 +11951,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4234</v>
+        <v>0.4219</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>165</v>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12017,10 +12017,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5766</v>
+        <v>0.5781000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>170</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5106999999999999</v>
+        <v>0.5097</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>-104</v>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4893</v>
+        <v>0.4903</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>104</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12215,13 +12215,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.46995</v>
+        <v>0.47645</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.44285</v>
+        <v>0.43635</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12347,13 +12347,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4663</v>
+        <v>0.4611</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +114). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12413,13 +12413,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5337</v>
+        <v>0.5389</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12551,7 +12551,7 @@
         <v>122</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12617,7 +12617,7 @@
         <v>167</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12743,13 +12743,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4346</v>
+        <v>0.4389</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5654</v>
+        <v>0.5611</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12875,13 +12875,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.501</v>
+        <v>0.5011</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-100</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12941,13 +12941,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.499</v>
+        <v>0.4989</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>100</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -13007,13 +13007,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4232</v>
+        <v>0.4335</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13073,13 +13073,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5768</v>
+        <v>0.5665</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-136</v>
+        <v>-131</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3956</v>
+        <v>0.3807</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13205,13 +13205,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6044</v>
+        <v>0.6193</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-153</v>
+        <v>-163</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-163</v>
+        <v>-178</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13271,13 +13271,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.42785</v>
+        <v>0.43055</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13337,13 +13337,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5721499999999999</v>
+        <v>0.56945</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3881</v>
+        <v>0.4446</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13469,13 +13469,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6119</v>
+        <v>0.5554</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-158</v>
+        <v>-125</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>112</v>
+        <v>-113</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13535,10 +13535,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4685</v>
+        <v>0.4659</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>130</v>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5315</v>
+        <v>0.5341</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>-133</v>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.44275</v>
+        <v>0.43045</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.55725</v>
+        <v>0.48275</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-126</v>
+        <v>107</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13799,13 +13799,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.294</v>
+        <v>0.3024</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 29.4% (fair +240). Your call.</t>
+          <t>Model 30.2% (fair +231). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13865,13 +13865,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.706</v>
+        <v>0.6976</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-240</v>
+        <v>-231</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 70.6% (fair -240). Your call.</t>
+          <t>Model 69.8% (fair -231). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13931,13 +13931,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4359</v>
+        <v>0.4306</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13997,13 +13997,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5641</v>
+        <v>0.5694</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-111</v>
+        <v>-117</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14063,13 +14063,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5246</v>
+        <v>0.5062</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-110</v>
+        <v>-103</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14129,13 +14129,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4754</v>
+        <v>0.4938</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>127</v>
+        <v>-104</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4485</v>
+        <v>0.4299</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>178</v>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5515</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-123</v>
+        <v>-133</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>178</v>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4525</v>
+        <v>0.4535</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>121</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.4% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5475</v>
+        <v>0.5465</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>-121</v>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14455,10 +14455,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5653</v>
+        <v>0.5585</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4347</v>
+        <v>0.4415</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.4509</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5491</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-118</v>
+        <v>-122</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14711,10 +14711,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4998</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14775,10 +14775,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5002</v>
+        <v>0.4995</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4201</v>
+        <v>0.4202</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>138</v>
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5799</v>
+        <v>0.5798</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>-138</v>
@@ -15171,7 +15171,7 @@
         <v>-114</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -15231,13 +15231,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.6198</v>
+        <v>0.6228</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-165</v>
+        <v>-156</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15297,13 +15297,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.3802</v>
+        <v>0.3772</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15567,7 +15567,7 @@
         <v>-136</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15627,13 +15627,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.3934</v>
+        <v>0.3831</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +154). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15693,10 +15693,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.6066</v>
+        <v>0.6169</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-154</v>
+        <v>-161</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>-155</v>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5039</v>
+        <v>0.5067999999999999</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4961</v>
+        <v>0.4932</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>114</v>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16019,17 +16019,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4572</v>
+        <v>0.528</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>119</v>
+        <v>-112</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16053,7 +16053,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16085,17 +16085,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4561999999999999</v>
+        <v>0.472</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16155,13 +16155,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5946</v>
+        <v>0.5879</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-147</v>
+        <v>-143</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16221,13 +16221,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4054</v>
+        <v>0.4121</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4415096000000001</v>
+        <v>0.4431224000000001</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>126</v>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5584903999999999</v>
+        <v>0.5568775999999999</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>-126</v>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16419,13 +16419,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.44635</v>
+        <v>0.43935</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16485,13 +16485,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.55365</v>
+        <v>0.56065</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-124</v>
+        <v>-128</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-105</v>
+        <v>117</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.379</v>
+        <v>0.3777</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16581,7 +16581,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16617,13 +16617,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.621</v>
+        <v>0.6223000000000001</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16683,10 +16683,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4614</v>
+        <v>0.4588</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>117</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16749,13 +16749,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5386</v>
+        <v>0.5412</v>
       </c>
       <c r="G98" s="14" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H98" s="15" t="n">
         <v>-117</v>
-      </c>
-      <c r="H98" s="15" t="n">
-        <v>-113</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.484</v>
+        <v>0.4822</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>107</v>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16881,13 +16881,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.516</v>
+        <v>0.5178</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>-107</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16947,13 +16947,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.3482</v>
+        <v>0.3492</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 34.8% (fair +187). Your call.</t>
+          <t>Model 34.9% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17013,13 +17013,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.6517999999999999</v>
+        <v>0.6508</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-187</v>
+        <v>-186</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 65.2% (fair -187). Your call.</t>
+          <t>Model 65.1% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17079,13 +17079,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4241</v>
+        <v>0.429</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17145,13 +17145,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5759</v>
+        <v>0.571</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-136</v>
+        <v>-133</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17211,10 +17211,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4912</v>
+        <v>0.51875</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>-105</v>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17277,13 +17277,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4228999999999999</v>
+        <v>0.3947499999999999</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.3956</v>
+        <v>0.3829</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +153). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17409,13 +17409,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.6044</v>
+        <v>0.6171</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-153</v>
+        <v>-161</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-155</v>
+        <v>-165</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -153). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17475,13 +17475,13 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.499</v>
+        <v>0.515</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17505,7 +17505,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17541,13 +17541,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.501</v>
+        <v>0.485</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-100</v>
+        <v>106</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17571,7 +17571,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17588,32 +17588,32 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.7308</v>
+        <v>0.4964</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-271</v>
+        <v>101</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-138</v>
+        <v>-105</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17637,7 +17637,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 73.1% (fair -271). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17654,32 +17654,32 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.2692</v>
+        <v>0.5036</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>271</v>
+        <v>-101</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>144</v>
+        <v>-102</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 26.9% (fair +271). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17720,32 +17720,32 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4717</v>
+        <v>0.5823</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>112</v>
+        <v>-139</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>117</v>
+        <v>-130</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17786,32 +17786,32 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.4177</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-112</v>
+        <v>139</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-120</v>
+        <v>120</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17862,22 +17862,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4641</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>115</v>
+        <v>-281</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-110</v>
+        <v>-144</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 73.7% (fair -281). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17928,22 +17928,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5359</v>
+        <v>0.2626</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-115</v>
+        <v>281</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-105</v>
+        <v>150</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 26.3% (fair +281). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17984,32 +17984,32 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5263</v>
+        <v>0.4957</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-111</v>
+        <v>102</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18033,7 +18033,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18050,32 +18050,32 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4737</v>
+        <v>0.5043</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>111</v>
+        <v>-102</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18099,7 +18099,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18116,32 +18116,32 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4917</v>
+        <v>0.4637</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18182,32 +18182,32 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5083</v>
+        <v>0.5363</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-103</v>
+        <v>-116</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18258,22 +18258,22 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.585</v>
+        <v>0.5252</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-141</v>
+        <v>-111</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-155</v>
+        <v>-122</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18324,22 +18324,22 @@
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.415</v>
+        <v>0.4748</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18380,31 +18380,33 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5016</v>
+        <v>0.5099</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H123" s="15" t="n"/>
+        <v>-104</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
         <v/>
@@ -18427,7 +18429,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18444,31 +18446,33 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4984</v>
+        <v>0.4901</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="H124" s="15" t="n"/>
+        <v>104</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-108</v>
+      </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
         <v/>
@@ -18491,7 +18495,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18508,32 +18512,32 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.5149</v>
+        <v>0.5868</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>-106</v>
+        <v>-142</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>105</v>
+        <v>-150</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18557,7 +18561,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18574,32 +18578,32 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4851</v>
+        <v>0.4132</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-104</v>
+        <v>138</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18623,7 +18627,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18650,23 +18654,21 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.3664</v>
+        <v>0.5016</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>173</v>
-      </c>
-      <c r="H127" s="15" t="n">
-        <v>162</v>
-      </c>
+        <v>-101</v>
+      </c>
+      <c r="H127" s="15" t="n"/>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
         <v/>
@@ -18689,7 +18691,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18716,23 +18718,21 @@
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6335999999999999</v>
+        <v>0.4984</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-173</v>
-      </c>
-      <c r="H128" s="15" t="n">
-        <v>-170</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H128" s="15" t="n"/>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
         <v/>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18772,31 +18772,33 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4377</v>
+        <v>0.5630500000000001</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>128</v>
-      </c>
-      <c r="H129" s="15" t="n"/>
+        <v>-129</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
         <v/>
@@ -18819,7 +18821,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18836,31 +18838,33 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5623</v>
+        <v>0.4369499999999999</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H130" s="15" t="n"/>
+        <v>129</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-104</v>
+      </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
         <v/>
@@ -18883,7 +18887,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18900,32 +18904,32 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.5172</v>
+        <v>0.3618</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>-107</v>
+        <v>176</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>-120</v>
+        <v>170</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18949,7 +18953,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18966,32 +18970,32 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4828</v>
+        <v>0.6382</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>107</v>
+        <v>-176</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>100</v>
+        <v>-170</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19015,7 +19019,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19042,23 +19046,21 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres -1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.3805</v>
+        <v>0.4442</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>163</v>
-      </c>
-      <c r="H133" s="15" t="n">
-        <v>168</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="H133" s="15" t="n"/>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
         <v/>
@@ -19081,7 +19083,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19108,23 +19110,21 @@
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.6194999999999999</v>
+        <v>0.5558</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>-163</v>
-      </c>
-      <c r="H134" s="15" t="n">
-        <v>-185</v>
-      </c>
+        <v>-125</v>
+      </c>
+      <c r="H134" s="15" t="n"/>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
         <v/>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -163). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19183,10 +19183,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4647</v>
+        <v>0.4615</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H135" s="15" t="n"/>
       <c r="I135" s="13">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19247,10 +19247,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5353</v>
+        <v>0.5385</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="H136" s="15" t="n"/>
       <c r="I136" s="13">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7143999999999999</v>
+        <v>0.7132000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-250</v>
+        <v>-249</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-300</v>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.4% (fair -250). Your call.</t>
+          <t>Model 71.3% (fair -249). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -19518,13 +19518,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2856</v>
+        <v>0.2868</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -19548,7 +19548,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 28.6% (fair +250). Your call.</t>
+          <t>Model 28.7% (fair +249). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5848</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-141</v>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -141). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19650,13 +19650,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4157999999999999</v>
+        <v>0.4152</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>141</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +141). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19722,7 +19722,7 @@
         <v>-145</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -19788,7 +19788,7 @@
         <v>145</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -19848,13 +19848,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7246</v>
+        <v>0.7255</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-237</v>
+        <v>-244</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 72.5% (fair -263). Your call.</t>
+          <t>Model 72.5% (fair -264). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19914,10 +19914,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2754</v>
+        <v>0.2745</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>245</v>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 27.5% (fair +263). Your call.</t>
+          <t>Model 27.5% (fair +264). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19976,17 +19976,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>Over 168</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.53725850755538</v>
+        <v>0.5489231605870841</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-116</v>
+        <v>-122</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20042,14 +20042,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 168.5</t>
+          <t>Under 168</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.46274149244462</v>
+        <v>0.4277768394129159</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20184,7 +20184,7 @@
         <v>-400</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -20244,10 +20244,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7152000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-250</v>
+        <v>-251</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-217</v>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 71.4% (fair -250). Your call.</t>
+          <t>Model 71.5% (fair -251). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20310,13 +20310,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2858</v>
+        <v>0.2848</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 28.6% (fair +250). Your call.</t>
+          <t>Model 28.5% (fair +251). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20448,7 +20448,7 @@
         <v>131</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -20580,7 +20580,7 @@
         <v>-245</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -20772,13 +20772,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5382</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -20838,10 +20838,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4618</v>
+        <v>0.4641999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-104</v>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -20904,13 +20904,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.4691</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -20970,13 +20970,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5308999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -21042,7 +21042,7 @@
         <v>-209</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
